--- a/data/dados_gerais.xlsx
+++ b/data/dados_gerais.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\TEMERON\08. Projetos\Set Up English\2026_01_Gestão_de_Marca\#modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894770E7-0E96-4392-BA5B-67677A47197D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A25856B-6F05-4B34-898A-D044CC3B2B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Mês</t>
   </si>
@@ -60,13 +60,19 @@
   </si>
   <si>
     <t>Ano</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +84,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -430,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7CB945-887C-4107-986F-6574D1A3576A}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
@@ -486,7 +498,42 @@
         <v>18</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
+        <v>414</v>
+      </c>
+      <c r="D3" s="2">
+        <v>53</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>369</v>
+      </c>
+      <c r="D4" s="2">
+        <v>375</v>
+      </c>
+      <c r="E4" s="2">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
